--- a/data/trans_dic/P15B_tráfico-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15B_tráfico-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,36</t>
+          <t>0,0; 58,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,58; 64,04</t>
+          <t>29,1; 62,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,13; 53,44</t>
+          <t>11,43; 53,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,31; 71,45</t>
+          <t>23,78; 62,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,88</t>
+          <t>0,0; 77,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,07; 49,86</t>
+          <t>11,62; 51,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,26; 45,35</t>
+          <t>10,86; 45,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,0; 28,82</t>
+          <t>7,22; 26,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 47,9</t>
+          <t>5,55; 47,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,92; 51,89</t>
+          <t>27,37; 52,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,36; 42,18</t>
+          <t>15,47; 40,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,21; 52,43</t>
+          <t>17,32; 41,9</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,25; 100,0</t>
+          <t>55,24; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,27; 57,6</t>
+          <t>23,25; 57,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 41,98</t>
+          <t>5,54; 40,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,12; 61,88</t>
+          <t>12,13; 59,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,84; 68,79</t>
+          <t>9,8; 69,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,98; 38,44</t>
+          <t>6,7; 37,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 51,86</t>
+          <t>6,5; 54,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 30,92</t>
+          <t>8,1; 35,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,98; 80,06</t>
+          <t>30,68; 80,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,19; 42,55</t>
+          <t>18,77; 42,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,19; 38,46</t>
+          <t>9,24; 38,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,63; 40,89</t>
+          <t>14,51; 40,71</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,73; 61,89</t>
+          <t>12,33; 65,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 16,36</t>
+          <t>1,8; 18,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,02; 42,84</t>
+          <t>7,91; 41,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 32,96</t>
+          <t>2,92; 29,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 27,96</t>
+          <t>2,51; 27,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,51</t>
+          <t>0,0; 33,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 33,55</t>
+          <t>5,51; 33,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,01; 54,53</t>
+          <t>11,26; 55,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 17,66</t>
+          <t>4,11; 16,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 34,64</t>
+          <t>9,42; 34,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 27,64</t>
+          <t>6,71; 26,54</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>40,87%</t>
         </is>
       </c>
     </row>
@@ -1137,32 +1137,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,34</t>
+          <t>0,0; 33,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,7; 47,12</t>
+          <t>8,97; 46,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,32; 37,21</t>
+          <t>7,84; 35,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,34; 61,25</t>
+          <t>10,38; 61,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,6; 74,35</t>
+          <t>9,71; 68,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,55</t>
+          <t>0,0; 28,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,27 +1172,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,86; 77,71</t>
+          <t>27,5; 75,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 36,79</t>
+          <t>6,77; 37,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,94; 34,46</t>
+          <t>8,07; 33,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 19,54</t>
+          <t>4,63; 19,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,7; 59,82</t>
+          <t>21,4; 62,31</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,02</t>
+          <t>0,0; 42,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,01; 59,99</t>
+          <t>7,65; 59,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,37</t>
+          <t>0,0; 46,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,24</t>
+          <t>0,0; 54,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,76</t>
+          <t>0,0; 69,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,19; 68,43</t>
+          <t>24,35; 69,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 46,06</t>
+          <t>5,68; 42,11</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,63; 57,76</t>
+          <t>23,84; 58,74</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,7</t>
+          <t>0,0; 40,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,12</t>
+          <t>0,0; 53,49</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1422,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,25; 50,86</t>
+          <t>13,95; 49,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,53; 34,02</t>
+          <t>3,48; 32,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,47; 31,73</t>
+          <t>3,19; 27,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,52; 28,46</t>
+          <t>5,19; 27,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,6; 28,17</t>
+          <t>2,58; 25,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 16,58</t>
+          <t>1,27; 15,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,54; 32,0</t>
+          <t>10,76; 32,27</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,26; 22,68</t>
+          <t>4,33; 23,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,53; 17,83</t>
+          <t>3,63; 17,06</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,47; 47,71</t>
+          <t>13,46; 50,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,2; 22,57</t>
+          <t>6,28; 23,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,95; 46,62</t>
+          <t>12,39; 49,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20,49; 51,24</t>
+          <t>22,77; 50,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,42; 44,33</t>
+          <t>5,39; 43,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,34; 29,59</t>
+          <t>8,56; 27,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,43; 58,98</t>
+          <t>20,41; 60,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,44; 36,35</t>
+          <t>10,84; 35,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,41; 39,32</t>
+          <t>13,64; 38,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,45; 22,46</t>
+          <t>9,68; 22,19</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21,07; 47,69</t>
+          <t>22,39; 48,33</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,87; 36,32</t>
+          <t>19,4; 38,71</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>34,39; 74,34</t>
+          <t>32,33; 72,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,08; 64,64</t>
+          <t>22,19; 65,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,16; 39,36</t>
+          <t>9,21; 39,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,51; 33,94</t>
+          <t>3,75; 34,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,87; 40,22</t>
+          <t>8,04; 38,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,15; 36,11</t>
+          <t>4,24; 35,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,92; 37,02</t>
+          <t>7,1; 39,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,58; 51,94</t>
+          <t>21,37; 52,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24,11; 49,46</t>
+          <t>24,2; 51,71</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16,78; 43,15</t>
+          <t>16,4; 43,76</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11,35; 31,4</t>
+          <t>11,15; 32,74</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,86; 37,81</t>
+          <t>15,32; 35,67</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24,44; 42,65</t>
+          <t>23,93; 41,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20,63; 31,13</t>
+          <t>20,01; 31,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,9; 27,73</t>
+          <t>15,98; 28,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,85; 35,57</t>
+          <t>20,99; 34,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,73; 29,85</t>
+          <t>13,58; 30,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,06; 24,24</t>
+          <t>13,89; 24,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,32; 23,19</t>
+          <t>12,07; 23,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16,84; 28,19</t>
+          <t>16,69; 28,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21,43; 33,86</t>
+          <t>22,05; 34,92</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18,81; 26,05</t>
+          <t>19,02; 26,6</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15,52; 23,7</t>
+          <t>15,93; 23,57</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,76; 29,46</t>
+          <t>20,02; 29,06</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18056</t>
+          <t>16033</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4680</t>
+          <t>0; 5470</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11326; 23718</t>
+          <t>10776; 23124</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2521; 10264</t>
+          <t>2196; 10199</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6549; 20071</t>
+          <t>6429; 16984</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5237</t>
+          <t>0; 5458</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3885; 13774</t>
+          <t>3210; 14103</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3400; 13691</t>
+          <t>3277; 13604</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2319; 8351</t>
+          <t>2196; 8130</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>900; 7847</t>
+          <t>909; 7713</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17407; 33550</t>
+          <t>17700; 34259</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8082; 20832</t>
+          <t>7642; 20189</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10964; 29920</t>
+          <t>9956; 24080</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14183</t>
+          <t>14794</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3317; 7852</t>
+          <t>4338; 7852</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7452; 18450</t>
+          <t>7445; 18321</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1012; 7706</t>
+          <t>1017; 7478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3193; 15065</t>
+          <t>2998; 14722</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>882; 6166</t>
+          <t>878; 6195</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2113; 11631</t>
+          <t>2027; 11203</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1041; 8235</t>
+          <t>1033; 8673</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2532; 10317</t>
+          <t>2814; 12211</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5209; 13462</t>
+          <t>5159; 13614</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11332; 26499</t>
+          <t>11689; 26339</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3148; 13168</t>
+          <t>3164; 13341</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7290; 23597</t>
+          <t>8622; 24195</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>6894</t>
         </is>
       </c>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2684; 11281</t>
+          <t>2247; 11883</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>950; 8647</t>
+          <t>951; 9699</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1862; 9951</t>
+          <t>1837; 9549</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>615; 7030</t>
+          <t>651; 6611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,37 +2650,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1066; 11439</t>
+          <t>1029; 11405</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4652</t>
+          <t>0; 4653</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1394; 8990</t>
+          <t>1472; 8964</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2471; 12233</t>
+          <t>2527; 12346</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3987; 16558</t>
+          <t>3856; 15888</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3493; 12856</t>
+          <t>3495; 12797</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3672; 13304</t>
+          <t>3287; 13007</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9774</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>19412</t>
         </is>
       </c>
     </row>
@@ -2833,32 +2833,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6654</t>
+          <t>0; 5985</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3081; 14967</t>
+          <t>2850; 14838</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3195; 14285</t>
+          <t>3010; 13674</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1507; 14548</t>
+          <t>2917; 17304</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>940; 7281</t>
+          <t>950; 6676</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5327</t>
+          <t>0; 5036</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2868,27 +2868,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4709; 14152</t>
+          <t>5335; 14724</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1922; 10158</t>
+          <t>1870; 10300</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3904; 16956</t>
+          <t>3973; 16554</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2939; 14610</t>
+          <t>3462; 14826</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8268; 25103</t>
+          <t>10162; 29595</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1640</t>
         </is>
       </c>
     </row>
@@ -3041,32 +3041,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4027</t>
+          <t>0; 3099</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>923; 7902</t>
+          <t>1008; 7872</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4796</t>
+          <t>0; 4700</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3787</t>
+          <t>0; 4113</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5445</t>
+          <t>0; 5435</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4788; 13548</t>
+          <t>4821; 13676</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3081,22 +3081,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>864; 6966</t>
+          <t>859; 6369</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8121; 19043</t>
+          <t>7861; 19367</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5672</t>
+          <t>0; 5931</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 4065</t>
+          <t>0; 4287</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4582</t>
         </is>
       </c>
     </row>
@@ -3254,17 +3254,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4020; 15438</t>
+          <t>4235; 14894</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>967; 9326</t>
+          <t>955; 9017</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>903; 8260</t>
+          <t>831; 7178</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3274,17 +3274,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1953; 10079</t>
+          <t>1838; 9781</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>949; 10269</t>
+          <t>941; 9397</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>344; 4477</t>
+          <t>356; 4437</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3294,17 +3294,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7590; 21044</t>
+          <t>7077; 21224</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2724; 14486</t>
+          <t>2768; 14836</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1870; 9457</t>
+          <t>1966; 9238</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14512</t>
+          <t>19687</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>11703</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>24708</t>
+          <t>31390</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4220; 13017</t>
+          <t>3672; 13656</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4079; 14837</t>
+          <t>4127; 15734</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3160; 12326</t>
+          <t>3274; 13160</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8901; 22257</t>
+          <t>12707; 28069</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>998; 8164</t>
+          <t>993; 8076</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4893; 17357</t>
+          <t>5021; 15981</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5873; 16166</t>
+          <t>5595; 16448</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5233; 18213</t>
+          <t>6333; 20538</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6584; 17971</t>
+          <t>6235; 17527</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11754; 27941</t>
+          <t>12048; 27605</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11343; 25677</t>
+          <t>12056; 26020</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16713; 33977</t>
+          <t>22157; 44224</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>10552</t>
+          <t>11860</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>15636</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>9074; 19619</t>
+          <t>8533; 19120</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5782; 15521</t>
+          <t>5328; 15648</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3169; 13621</t>
+          <t>3187; 13773</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>878; 8494</t>
+          <t>1066; 9779</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2118; 10833</t>
+          <t>2166; 10345</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1050; 9140</t>
+          <t>1074; 8865</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1849; 9897</t>
+          <t>1900; 10652</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6461; 14862</t>
+          <t>7228; 17808</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>12855; 26373</t>
+          <t>12905; 27571</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8277; 21283</t>
+          <t>8089; 21587</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6962; 19262</t>
+          <t>6842; 20082</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>9044; 20279</t>
+          <t>9539; 22212</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>53226</t>
+          <t>59357</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>46973</t>
+          <t>51025</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>100199</t>
+          <t>110382</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>30076; 52497</t>
+          <t>29457; 50560</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>59210; 89346</t>
+          <t>57422; 89055</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31443; 54840</t>
+          <t>31603; 56501</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39525; 70825</t>
+          <t>46168; 76711</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>12875; 28002</t>
+          <t>12735; 28731</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35916; 61910</t>
+          <t>35480; 61417</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23578; 44404</t>
+          <t>23115; 44219</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>35970; 60207</t>
+          <t>38760; 66540</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>46470; 73427</t>
+          <t>47830; 75745</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>102019; 141291</t>
+          <t>103161; 144262</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>60415; 92239</t>
+          <t>61994; 91738</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>81571; 121571</t>
+          <t>90501; 131372</t>
         </is>
       </c>
     </row>
